--- a/matriz_auditoria.xlsx
+++ b/matriz_auditoria.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mribeiro1\MARINGA TURISMO\Maringá Turismo - PLANEJAMENTO ESTRATEGICO (1)\01-Planejamento Estratégico\Ferramenta de Controle - Compliance\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FCAE3C-A7D7-4A8D-8323-06AB19474270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>ID</t>
   </si>
@@ -75,213 +81,12 @@
   <si>
     <t>Timeline_JSON</t>
   </si>
-  <si>
-    <t>AUD-01</t>
-  </si>
-  <si>
-    <t>AUD-02</t>
-  </si>
-  <si>
-    <t>AUD-03</t>
-  </si>
-  <si>
-    <t>AUD-04</t>
-  </si>
-  <si>
-    <t>AUD-05</t>
-  </si>
-  <si>
-    <t>São Paulo - HQ</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Rio de Janeiro</t>
-  </si>
-  <si>
-    <t>Curitiba</t>
-  </si>
-  <si>
-    <t>Geral</t>
-  </si>
-  <si>
-    <t>Caixa</t>
-  </si>
-  <si>
-    <t>Crédito</t>
-  </si>
-  <si>
-    <t>Segurança</t>
-  </si>
-  <si>
-    <t>Processos</t>
-  </si>
-  <si>
-    <t>Compliance</t>
-  </si>
-  <si>
-    <t>Divergência no fechamento físico de caixa</t>
-  </si>
-  <si>
-    <t>Falta de assinatura em contrato de cliente corporativo</t>
-  </si>
-  <si>
-    <t>Câmera de CFTV inoperante na tesouraria</t>
-  </si>
-  <si>
-    <t>Treinamento de compliance pendente</t>
-  </si>
-  <si>
-    <t>Teste</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Crítica</t>
-  </si>
-  <si>
-    <t>Média</t>
-  </si>
-  <si>
-    <t>Baixa</t>
-  </si>
-  <si>
-    <t>Realizar contagem diária e redefinir alçada.</t>
-  </si>
-  <si>
-    <t>Coletar assinatura pendente ou reter crédito.</t>
-  </si>
-  <si>
-    <t>Trocar equipamento de gravação CFTV.</t>
-  </si>
-  <si>
-    <t>Agendar treinamento para equipe.</t>
-  </si>
-  <si>
-    <t>nada</t>
-  </si>
-  <si>
-    <t>Operações</t>
-  </si>
-  <si>
-    <t>Risco/Crédito</t>
-  </si>
-  <si>
-    <t>Infraestrutura</t>
-  </si>
-  <si>
-    <t>Recursos Humanos</t>
-  </si>
-  <si>
-    <t>Carlos Silva</t>
-  </si>
-  <si>
-    <t>Ana Souza</t>
-  </si>
-  <si>
-    <t>João Lima</t>
-  </si>
-  <si>
-    <t>Fernanda Costa</t>
-  </si>
-  <si>
-    <t>Lucian</t>
-  </si>
-  <si>
-    <t>carlos@maringaturismo.com.br</t>
-  </si>
-  <si>
-    <t>ana@maringaturismo.com.br</t>
-  </si>
-  <si>
-    <t>joao@maringaturismo.com.br</t>
-  </si>
-  <si>
-    <t>fernanda@maringaturismo.com.br</t>
-  </si>
-  <si>
-    <t>llljml@mmmhjk.com.br</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>2026-09-10</t>
-  </si>
-  <si>
-    <t>2026-10-01</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>Concluído</t>
-  </si>
-  <si>
-    <t>Em Andamento</t>
-  </si>
-  <si>
-    <t>A Fazer</t>
-  </si>
-  <si>
-    <t>AUD-01_Captura de tela 2026-09-04 095357.png</t>
-  </si>
-  <si>
-    <t>Nenhuma</t>
-  </si>
-  <si>
-    <t>laudo_cftv.pdf</t>
-  </si>
-  <si>
-    <t>nova</t>
-  </si>
-  <si>
-    <t>sdad</t>
-  </si>
-  <si>
-    <t>Troca realizada dia 02/09</t>
-  </si>
-  <si>
-    <t>São Paulo - HQ - Projeto Geral</t>
-  </si>
-  <si>
-    <t>Maringá - Projeto Geral</t>
-  </si>
-  <si>
-    <t>Rio de Janeiro - Projeto Geral</t>
-  </si>
-  <si>
-    <t>Curitiba - Projeto Geral</t>
-  </si>
-  <si>
-    <t>Cliente Corporativo - 122</t>
-  </si>
-  <si>
-    <t>2026-09-04</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>[]</t>
-  </si>
-  <si>
-    <t>[{"Data": "04/09/2026 16:58", "Nome": "Marcos Ribeiro (Master)", "Usuario": "mribeiro1", "Texto": "asdfasdf"}, {"Data": "04/09/2026 16:58", "Nome": "Marcos Ribeiro (Master)", "Usuario": "mribeiro1", "Texto": "sdfsdafdsa"}]</t>
-  </si>
-  <si>
-    <t>[{"Data": "04/09/2026 17:09", "Nome": "Marcos Ribeiro (Master)", "Usuario": "mribeiro1", "Texto": "asdfasdf", "Anexo": "AUD-02_20260904_170955_Captura de tela 2026-09-03 170415.png"}]</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,13 +123,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -362,7 +175,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -396,6 +209,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -430,9 +244,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -605,11 +420,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,301 +484,6 @@
       </c>
       <c r="T1" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L2" t="s">
-        <v>71</v>
-      </c>
-      <c r="M2" t="s">
-        <v>74</v>
-      </c>
-      <c r="N2" t="s">
-        <v>77</v>
-      </c>
-      <c r="O2" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>83</v>
-      </c>
-      <c r="R2" t="s">
-        <v>84</v>
-      </c>
-      <c r="S2" t="s">
-        <v>84</v>
-      </c>
-      <c r="T2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" t="s">
-        <v>64</v>
-      </c>
-      <c r="K3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L3" t="s">
-        <v>72</v>
-      </c>
-      <c r="M3" t="s">
-        <v>75</v>
-      </c>
-      <c r="N3" t="s">
-        <v>78</v>
-      </c>
-      <c r="O3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>83</v>
-      </c>
-      <c r="R3" t="s">
-        <v>84</v>
-      </c>
-      <c r="S3" t="s">
-        <v>85</v>
-      </c>
-      <c r="T3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K4" t="s">
-        <v>68</v>
-      </c>
-      <c r="L4" t="s">
-        <v>73</v>
-      </c>
-      <c r="M4" t="s">
-        <v>76</v>
-      </c>
-      <c r="N4" t="s">
-        <v>79</v>
-      </c>
-      <c r="O4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P4" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>83</v>
-      </c>
-      <c r="R4" t="s">
-        <v>84</v>
-      </c>
-      <c r="S4" t="s">
-        <v>84</v>
-      </c>
-      <c r="T4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I5" t="s">
-        <v>61</v>
-      </c>
-      <c r="J5" t="s">
-        <v>66</v>
-      </c>
-      <c r="K5" t="s">
-        <v>70</v>
-      </c>
-      <c r="L5" t="s">
-        <v>72</v>
-      </c>
-      <c r="N5" t="s">
-        <v>80</v>
-      </c>
-      <c r="O5" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>83</v>
-      </c>
-      <c r="R5" t="s">
-        <v>84</v>
-      </c>
-      <c r="S5" t="s">
-        <v>84</v>
-      </c>
-      <c r="T5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" t="s">
-        <v>62</v>
-      </c>
-      <c r="J6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K6" t="s">
-        <v>70</v>
-      </c>
-      <c r="N6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O6" t="s">
-        <v>29</v>
-      </c>
-      <c r="P6" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>83</v>
-      </c>
-      <c r="T6" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -972,6 +492,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100679A9D6214E23F41806BF79AA97D961D" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="615285cd3b9bba93d383710380480058">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c6f2750a-443f-47f1-aeea-95bbc8068025" xmlns:ns3="06f4cf46-f048-460d-8a19-e2350c45d0c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="450288bfee094da864ded7851c9db2e7" ns2:_="" ns3:_="">
     <xsd:import namespace="c6f2750a-443f-47f1-aeea-95bbc8068025"/>
@@ -1184,15 +713,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1205,13 +725,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EDD00AF-5A98-49CA-A105-1D73840BCE53}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88557B49-4CDD-441F-B027-1425DCEA0A50}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88557B49-4CDD-441F-B027-1425DCEA0A50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EDD00AF-5A98-49CA-A105-1D73840BCE53}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c6f2750a-443f-47f1-aeea-95bbc8068025"/>
+    <ds:schemaRef ds:uri="06f4cf46-f048-460d-8a19-e2350c45d0c5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17938C3F-B6B2-4267-86D2-B29DE3418224}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17938C3F-B6B2-4267-86D2-B29DE3418224}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="06f4cf46-f048-460d-8a19-e2350c45d0c5"/>
+    <ds:schemaRef ds:uri="c6f2750a-443f-47f1-aeea-95bbc8068025"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>